--- a/tests/workbooktests/workbooks/test_cashflows.xlsx
+++ b/tests/workbooktests/workbooks/test_cashflows.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09FD7F5-5D16-4F3E-9B99-EC8AB9FA2F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEEDB6C-0F13-42C7-908D-0D123244D08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="-19800" windowWidth="28800" windowHeight="18120" activeTab="2" xr2:uid="{27232A84-7D6C-4EF7-8EDD-D20622985291}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{27232A84-7D6C-4EF7-8EDD-D20622985291}"/>
   </bookViews>
   <sheets>
     <sheet name="EvaluationDate" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1220,24 +1220,11 @@
       </c>
       <c r="B25" t="str" cm="1">
         <f t="array" ref="B25">_xll.qlCappedFlooredIborCoupon(B17,B8,B15,B16,2,B6,,,B11)</f>
-        <v>欣[test_cashflows.xlsx]Coupons!R25C2CappedFlooredIborCoupon,J</v>
+        <v>欣[test_cashflows.xlsx]Coupons!R25C2CappedFlooredIborCoupon,A</v>
       </c>
       <c r="C25" s="1" cm="1">
         <f t="array" ref="C25">_xll.qlCashFlowDate(B25)</f>
         <v>46332</v>
-      </c>
-      <c r="D25" t="str" cm="1">
-        <f t="array" ref="D25">_xll.qlCashFlowAmount(B25)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: pricer not set
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlibxloil\cashflows.py", line 152, in qlCashFlowAmount
-    return cashflow.amount()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 13464, in amount
-    return _QuantLib.CashFlow_amount(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: pricer not set
-</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -2488,36 +2475,18 @@
       <c r="A82" t="s">
         <v>109</v>
       </c>
-      <c r="B82" t="str" cm="1">
-        <f t="array" ref="B82">_xll.qlCappedFlooredOvernightIndexedCouponEffectiveCapletVolatility(B26)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: coupon pricer not an instance of OvernightIndexedCouponPricer
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlibxloil\cashflows.py", line 777, in qlCappedFlooredOvernightIndexedCouponEffectiveCapletVolatility
-    return coupon.effectiveCapletVolatility()
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 14225, in effectiveCapletVolatility
-    return _QuantLib.CappedFlooredOvernightIndexedCoupon_effectiveCapletVolatility(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: coupon pricer not an instance of OvernightIndexedCouponPricer
-</v>
+      <c r="B82" cm="1">
+        <f t="array" ref="B82">FIND("RuntimeError: RuntimeError: coupon pricer not an instance of OvernightIndexedCouponPricer", _xll.qlCappedFlooredOvernightIndexedCouponEffectiveCapletVolatility(B26))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>110</v>
       </c>
-      <c r="B83" t="str" cm="1">
-        <f t="array" ref="B83">_xll.qlCappedFlooredOvernightIndexedCouponEffectiveFloorletVolatility(B26)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: coupon pricer not an instance of OvernightIndexedCouponPricer
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlibxloil\cashflows.py", line 791, in qlCappedFlooredOvernightIndexedCouponEffectiveFloorletVolatility
-    return coupon.effectiveFloorletVolatility()
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 14229, in effectiveFloorletVolatility
-    return _QuantLib.CappedFlooredOvernightIndexedCoupon_effectiveFloorletVolatility(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: coupon pricer not an instance of OvernightIndexedCouponPricer
-</v>
+      <c r="B83" cm="1">
+        <f t="array" ref="B83">FIND("RuntimeError: RuntimeError: coupon pricer not an instance of OvernightIndexedCouponPricer",_xll.qlCappedFlooredOvernightIndexedCouponEffectiveFloorletVolatility(B26))</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2950,7 +2919,7 @@
       </c>
       <c r="B28" cm="1">
         <f t="array" ref="B28">_xll.qlCashFlowsNpv(B20,B4,TRUE)</f>
-        <v>0.75984966644127827</v>
+        <v>0.75897582173628064</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
@@ -2959,7 +2928,7 @@
       </c>
       <c r="B29" cm="1">
         <f t="array" ref="B29">_xll.qlCashFlowsBps(B20,B4,TRUE)</f>
-        <v>2.5328322214709133E-3</v>
+        <v>2.5299194057875878E-3</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
@@ -2968,7 +2937,7 @@
       </c>
       <c r="B30" cm="1">
         <f t="array" ref="B30">_xll.qlCashFlowsNpv(_xlfn.ANCHORARRAY(B20),B4,TRUE)</f>
-        <v>4.3461326497866892</v>
+        <v>4.3411344966375012</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
@@ -2977,7 +2946,7 @@
       </c>
       <c r="B31" cm="1">
         <f t="array" ref="B31">_xll.qlCashFlowsBps(_xlfn.ANCHORARRAY(B20),B4,TRUE)</f>
-        <v>2.0464247138198152E-2</v>
+        <v>2.0440712780293871E-2</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
@@ -2986,12 +2955,12 @@
       </c>
       <c r="B32" cm="1">
         <f t="array" ref="B32:B33">_xll.qlCashFlowsNpvBps(_xlfn.ANCHORARRAY(B20),B4,TRUE)</f>
-        <v>4.3461326497866892</v>
+        <v>4.3411344966375012</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33">
-        <v>2.0464247138198152E-2</v>
+        <v>2.0440712780293871E-2</v>
       </c>
     </row>
   </sheetData>

--- a/tests/workbooktests/workbooks/test_cashflows.xlsx
+++ b/tests/workbooktests/workbooks/test_cashflows.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEEDB6C-0F13-42C7-908D-0D123244D08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABA26E1-E832-42FE-B6ED-A9F121C02EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{27232A84-7D6C-4EF7-8EDD-D20622985291}"/>
+    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{27232A84-7D6C-4EF7-8EDD-D20622985291}"/>
   </bookViews>
   <sheets>
     <sheet name="EvaluationDate" sheetId="3" r:id="rId1"/>
@@ -1089,7 +1089,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="1" cm="1">
-        <f t="array" ref="B14">_xll.qlCalendarAdvance("Target",B1,3,"Months","Following")</f>
+        <f t="array" ref="B14">_xll.qlCalendarAdvance2("Target",B1,3,"Months","Following")</f>
         <v>46238</v>
       </c>
     </row>
@@ -1448,9 +1448,9 @@
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B52" t="b" cm="1">
+      <c r="B52" t="str" cm="1">
         <f t="array" ref="B52">_xll.qlFloatingRateCouponSetPricer(B21,B51)</f>
-        <v>1</v>
+        <v>Error in arg 2 'pricer': Cannot convert '欣[test_cashflows.xlsx]Coupons!R51C2BlackIborCouponPricer,A': Expected cache string</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -2665,7 +2665,7 @@
         <v>21</v>
       </c>
       <c r="B13" s="1" cm="1">
-        <f t="array" ref="B13">_xll.qlCalendarAdvance2(B12,B1,"3m","following")</f>
+        <f t="array" ref="B13">_xll.qlCalendarAdvance(B12,B1,"3m","following")</f>
         <v>46238</v>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
         <v>22</v>
       </c>
       <c r="B14" s="1" cm="1">
-        <f t="array" ref="B14">_xll.qlCalendarAdvance2(B12,B13,"2y","following")</f>
+        <f t="array" ref="B14">_xll.qlCalendarAdvance(B12,B13,"2y","following")</f>
         <v>46969</v>
       </c>
     </row>
